--- a/artfynd/A 35848-2026 artfynd.xlsx
+++ b/artfynd/A 35848-2026 artfynd.xlsx
@@ -2054,6 +2054,11 @@
           <t>2026-08-05</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Sliten</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35848-2026 artfynd.xlsx
+++ b/artfynd/A 35848-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ37"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3161,10 +3161,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136363168</v>
+        <v>136751449</v>
       </c>
       <c r="B23" t="n">
-        <v>56927</v>
+        <v>56935</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3172,21 +3172,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>208257</v>
+        <v>208255</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3201,7 +3201,11 @@
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3239,12 +3243,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3271,38 +3275,38 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136363168</t>
+          <t>https://artportalen.se/Sighting/136751449</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>86590519</v>
+        <v>136363168</v>
       </c>
       <c r="B24" t="n">
-        <v>41972</v>
+        <v>56927</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>213797</v>
+        <v>208257</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Humlerotfjäril</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepialus humuli</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3313,20 +3317,12 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>ljusfälla</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Taleryd  (trädgård), Sm</t>
@@ -3363,12 +3359,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3395,13 +3391,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86590519</t>
+          <t>https://artportalen.se/Sighting/136363168</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113741497</v>
+        <v>86590519</v>
       </c>
       <c r="B25" t="n">
         <v>41972</v>
@@ -3435,13 +3431,17 @@
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>ljusfälla</t>
@@ -3453,13 +3453,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492342</v>
+        <v>492339</v>
       </c>
       <c r="R25" t="n">
         <v>6424648</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3483,12 +3483,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-06-09</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-06-09</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3515,52 +3515,56 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113741497</t>
+          <t>https://artportalen.se/Sighting/86590519</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117494358</v>
+        <v>113741497</v>
       </c>
       <c r="B26" t="n">
-        <v>40300</v>
+        <v>41972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>214803</v>
+        <v>213797</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Humlerotfjäril</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Hepialus humuli</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>pheromone</t>
+          <t>ljusfälla</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3599,12 +3603,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2023-06-09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2023-06-09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3631,13 +3635,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117494358</t>
+          <t>https://artportalen.se/Sighting/113741497</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117935757</v>
+        <v>117494358</v>
       </c>
       <c r="B27" t="n">
         <v>40300</v>
@@ -3667,15 +3671,11 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
@@ -3689,13 +3689,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492339</v>
+        <v>492342</v>
       </c>
       <c r="R27" t="n">
         <v>6424648</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3719,12 +3719,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3751,16 +3751,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117935757</t>
+          <t>https://artportalen.se/Sighting/117494358</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>101720738</v>
+        <v>117935757</v>
       </c>
       <c r="B28" t="n">
-        <v>40269</v>
+        <v>40300</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3768,26 +3768,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>214815</v>
+        <v>214803</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Större träfjäril</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cossus cossus</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -3800,7 +3800,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>ljusfälla</t>
+          <t>pheromone</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3871,13 +3871,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101720738</t>
+          <t>https://artportalen.se/Sighting/117935757</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>115237082</v>
+        <v>101720738</v>
       </c>
       <c r="B29" t="n">
         <v>40269</v>
@@ -3911,7 +3911,11 @@
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
@@ -3925,13 +3929,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492342</v>
+        <v>492339</v>
       </c>
       <c r="R29" t="n">
         <v>6424648</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3987,38 +3991,38 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115237082</t>
+          <t>https://artportalen.se/Sighting/101720738</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>101720697</v>
+        <v>115237082</v>
       </c>
       <c r="B30" t="n">
-        <v>43875</v>
+        <v>40269</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>215467</v>
+        <v>214815</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kvadratmott</t>
+          <t>Större träfjäril</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Udea olivalis</t>
+          <t>Cossus cossus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4027,11 +4031,7 @@
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
@@ -4045,13 +4045,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492339</v>
+        <v>492342</v>
       </c>
       <c r="R30" t="n">
         <v>6424648</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4107,13 +4107,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101720697</t>
+          <t>https://artportalen.se/Sighting/115237082</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113595554</v>
+        <v>101720697</v>
       </c>
       <c r="B31" t="n">
         <v>43875</v>
@@ -4141,9 +4141,17 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
@@ -4157,13 +4165,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492342</v>
+        <v>492339</v>
       </c>
       <c r="R31" t="n">
         <v>6424648</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4187,12 +4195,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4219,16 +4227,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113595554</t>
+          <t>https://artportalen.se/Sighting/101720697</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>115196117</v>
+        <v>113595554</v>
       </c>
       <c r="B32" t="n">
-        <v>41650</v>
+        <v>43875</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4236,21 +4244,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>215785</v>
+        <v>215467</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brunflammig fältmätare</t>
+          <t>Kvadratmott</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Perizoma flavofasciata</t>
+          <t>Udea olivalis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Thunberg, 1792)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4299,12 +4307,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-08-11</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-08-11</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4331,16 +4339,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115196117</t>
+          <t>https://artportalen.se/Sighting/113595554</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>114585493</v>
+        <v>115196117</v>
       </c>
       <c r="B33" t="n">
-        <v>42516</v>
+        <v>41650</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4348,21 +4356,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>216123</v>
+        <v>215785</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre stamfly</t>
+          <t>Brunflammig fältmätare</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Amphipoea crinanensis</t>
+          <t>Perizoma flavofasciata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Burrows, 1908)</t>
+          <t>(Thunberg, 1792)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4370,20 +4378,24 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>ljusfälla</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Taleryd  (trädgård), Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492339</v>
+        <v>492342</v>
       </c>
       <c r="R33" t="n">
         <v>6424648</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4407,12 +4419,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2021-08-02</t>
+          <t>2022-08-11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2021-08-02</t>
+          <t>2022-08-11</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4439,13 +4451,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114585493</t>
+          <t>https://artportalen.se/Sighting/115196117</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>115196067</v>
+        <v>114585493</v>
       </c>
       <c r="B34" t="n">
         <v>42516</v>
@@ -4478,24 +4490,20 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>ljusfälla</t>
-        </is>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Taleryd  (trädgård), Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492342</v>
+        <v>492339</v>
       </c>
       <c r="R34" t="n">
         <v>6424648</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4519,12 +4527,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-08-07</t>
+          <t>2021-08-02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-08-07</t>
+          <t>2021-08-02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4551,16 +4559,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115196067</t>
+          <t>https://artportalen.se/Sighting/114585493</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126438005</v>
+        <v>115196067</v>
       </c>
       <c r="B35" t="n">
-        <v>42691</v>
+        <v>42516</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4568,30 +4576,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>216164</v>
+        <v>216123</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Praktnejlikfly</t>
+          <t>Mindre stamfly</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hadena confusa</t>
+          <t>Amphipoea crinanensis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hufnagel, 1766)</t>
+          <t>(Burrows, 1908)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
@@ -4605,13 +4609,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492339</v>
+        <v>492342</v>
       </c>
       <c r="R35" t="n">
         <v>6424648</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4635,12 +4639,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2022-08-07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2022-08-07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4667,43 +4671,47 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126438005</t>
+          <t>https://artportalen.se/Sighting/115196067</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>115127604</v>
+        <v>126438005</v>
       </c>
       <c r="B36" t="n">
-        <v>42696</v>
+        <v>42691</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>216169</v>
+        <v>216164</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gulbrunt nejlikfly</t>
+          <t>Praktnejlikfly</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hadena perplexa</t>
+          <t>Hadena confusa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Hufnagel, 1766)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
@@ -4717,13 +4725,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492342</v>
+        <v>492339</v>
       </c>
       <c r="R36" t="n">
         <v>6424648</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4747,12 +4755,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4779,62 +4787,63 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115127604</t>
+          <t>https://artportalen.se/Sighting/126438005</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132204344</v>
+        <v>115127604</v>
       </c>
       <c r="B37" t="n">
-        <v>101324</v>
+        <v>42696</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222782</v>
+        <v>216169</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitsippa</t>
+          <t>Gulbrunt nejlikfly</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Anemone nemorosa</t>
+          <t>Hadena perplexa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>ljusfälla</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Taleryd  (trädgård), Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>492339</v>
+        <v>492342</v>
       </c>
       <c r="R37" t="n">
         <v>6424648</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4858,12 +4867,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2022-05-08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2022-05-08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4889,6 +4898,117 @@
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115127604</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>132204344</v>
+      </c>
+      <c r="B38" t="n">
+        <v>101324</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>222782</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vitsippa</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Anemone nemorosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Taleryd  (trädgård), Sm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>492339</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6424648</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Linderås</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132204344</t>
         </is>
@@ -4932,6 +5052,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35848-2026 artfynd.xlsx
+++ b/artfynd/A 35848-2026 artfynd.xlsx
@@ -1159,7 +1159,7 @@
         <v>136361538</v>
       </c>
       <c r="B6" t="n">
-        <v>45081</v>
+        <v>45083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>136609430</v>
       </c>
       <c r="B10" t="n">
-        <v>43250</v>
+        <v>43252</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>136609043</v>
       </c>
       <c r="B13" t="n">
-        <v>43359</v>
+        <v>43361</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>136362614</v>
       </c>
       <c r="B15" t="n">
-        <v>43289</v>
+        <v>43291</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>136362295</v>
       </c>
       <c r="B19" t="n">
-        <v>45074</v>
+        <v>45076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>136751449</v>
       </c>
       <c r="B23" t="n">
-        <v>56935</v>
+        <v>56937</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>136363168</v>
       </c>
       <c r="B24" t="n">
-        <v>56927</v>
+        <v>56929</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 35848-2026 artfynd.xlsx
+++ b/artfynd/A 35848-2026 artfynd.xlsx
@@ -1619,7 +1619,7 @@
         <v>136609430</v>
       </c>
       <c r="B10" t="n">
-        <v>43252</v>
+        <v>43265</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>136609043</v>
       </c>
       <c r="B13" t="n">
-        <v>43361</v>
+        <v>43374</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>136751449</v>
       </c>
       <c r="B23" t="n">
-        <v>56937</v>
+        <v>56950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 35848-2026 artfynd.xlsx
+++ b/artfynd/A 35848-2026 artfynd.xlsx
@@ -3164,7 +3164,7 @@
         <v>136751449</v>
       </c>
       <c r="B23" t="n">
-        <v>56950</v>
+        <v>56952</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 35848-2026 artfynd.xlsx
+++ b/artfynd/A 35848-2026 artfynd.xlsx
@@ -3195,17 +3195,9 @@
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>

--- a/artfynd/A 35848-2026 artfynd.xlsx
+++ b/artfynd/A 35848-2026 artfynd.xlsx
@@ -3164,7 +3164,7 @@
         <v>136751449</v>
       </c>
       <c r="B23" t="n">
-        <v>56952</v>
+        <v>56962</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 35848-2026 artfynd.xlsx
+++ b/artfynd/A 35848-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ38"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4897,43 +4897,44 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132204344</v>
+        <v>137353023</v>
       </c>
       <c r="B38" t="n">
-        <v>101324</v>
+        <v>42754</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222782</v>
+        <v>216169</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitsippa</t>
+          <t>Gulbrunt nejlikfly</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Anemone nemorosa</t>
+          <t>Hadena perplexa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>ljusfälla</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Taleryd  (trädgård), Sm</t>
@@ -4970,12 +4971,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5001,6 +5002,117 @@
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137353023</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>132204344</v>
+      </c>
+      <c r="B39" t="n">
+        <v>101324</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222782</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vitsippa</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Anemone nemorosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Taleryd  (trädgård), Sm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>492339</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6424648</v>
+      </c>
+      <c r="S39" t="n">
+        <v>4</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Linderås</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132204344</t>
         </is>
@@ -5045,6 +5157,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35848-2026 artfynd.xlsx
+++ b/artfynd/A 35848-2026 artfynd.xlsx
@@ -4900,7 +4900,7 @@
         <v>137353023</v>
       </c>
       <c r="B38" t="n">
-        <v>42754</v>
+        <v>42755</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
